--- a/eval/results/detailed_evaluation_new30.xlsx
+++ b/eval/results/detailed_evaluation_new30.xlsx
@@ -649,7 +649,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes"""</t>
         </is>
       </c>
       <c r="S2" t="n">
@@ -762,7 +762,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>Sanger sequencing"""</t>
         </is>
       </c>
       <c r="S3" t="n">
@@ -879,7 +879,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Plasma, DBS</t>
+          <t>Plasma, DBS"""</t>
         </is>
       </c>
       <c r="S4" t="n">
@@ -996,7 +996,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes"""</t>
         </is>
       </c>
       <c r="S5" t="n">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No"""</t>
         </is>
       </c>
       <c r="S6" t="n">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes"""</t>
         </is>
       </c>
       <c r="S7" t="n">
@@ -1347,11 +1347,11 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>NRTIs, INSTIs</t>
+          <t>Not reported"""</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1468,11 +1468,11 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>DTG, tenofovir, lamivudine, dolutegravir</t>
+          <t>Not reported"""</t>
         </is>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No"""</t>
         </is>
       </c>
       <c r="S10" t="n">
@@ -1706,7 +1706,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes"""</t>
         </is>
       </c>
       <c r="S11" t="n">
@@ -1823,11 +1823,11 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>PV008448-PV008641, PV407014-PV407203, and PV419497-PV419583</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1944,11 +1944,11 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>227"""</t>
         </is>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>Cameroon, Côte d'Ivoire, Malawi, Republic of Congo, Uganda, Zambia, and Zimbabwe</t>
+          <t>Cameroon, Cote d'Ivoire, Malawi, Republic of Congo, Uganda, Zambia, Zimbabwe"""</t>
         </is>
       </c>
       <c r="S14" t="n">
@@ -2182,7 +2182,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2022-2024</t>
+          <t>2022-2024"""</t>
         </is>
       </c>
       <c r="S15" t="n">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No"""</t>
         </is>
       </c>
       <c r="S16" t="n">
@@ -2416,7 +2416,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>IN, PR, RT</t>
+          <t>IN, PR, RT"""</t>
         </is>
       </c>
       <c r="S17" t="n">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>Tenofovir disoproxil maleate, emtricitabine</t>
+          <t>Tenofovir disoproxil fumarate/emtricitabine</t>
         </is>
       </c>
       <c r="S25" t="n">
@@ -3622,11 +3622,11 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="S27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Not reported</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S28" t="n">
@@ -4574,7 +4574,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>NGS</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S35" t="n">
@@ -4691,11 +4691,11 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>Plasma, Serum, PBMC</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4808,11 +4808,11 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4925,7 +4925,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S38" t="n">
@@ -5046,11 +5046,11 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5167,11 +5167,11 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>NRTIs, NNRTIs, PIs, INSTIs</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>Zidovudine, Didanosine, Abacavir, Tenofovir, Lopinavir, Atazanavir, Darunavir, Raltegravir, Dolutegravir, Elvitegravir, Bictegravir, Rilpivirine, Doravirine</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S41" t="n">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Not reported</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S44" t="n">
@@ -5875,11 +5875,11 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5992,11 +5992,11 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1994-2024</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6226,11 +6226,11 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>PR, RT, IN</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -7227,11 +7227,11 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7566,11 +7566,11 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>1667</t>
+          <t>1677</t>
         </is>
       </c>
       <c r="S61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7913,7 +7913,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S64" t="n">
@@ -8143,7 +8143,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>Yes.</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="S66" t="n">
@@ -8260,11 +8260,11 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>Sanger sequencing.</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8381,7 +8381,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>Plasma.</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="S68" t="n">
@@ -8498,7 +8498,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>Yes.</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="S69" t="n">
@@ -8619,7 +8619,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>No.</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S70" t="n">
@@ -8740,7 +8740,7 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>Yes.</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="S71" t="n">
@@ -8861,11 +8861,11 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>NNRTI, PI.</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8982,7 +8982,7 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>EFV, NVP, ATV/r, LPV/r.</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S73" t="n">
@@ -9104,7 +9104,7 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>No.</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S74" t="n">
@@ -9221,7 +9221,7 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>No.</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S75" t="n">
@@ -9580,7 +9580,7 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>Kenya.</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="S78" t="n">
@@ -9701,7 +9701,7 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>2011-2021.</t>
+          <t>2011-2021</t>
         </is>
       </c>
       <c r="S79" t="n">
@@ -9822,7 +9822,7 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>Not reported.</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S80" t="n">
@@ -9943,7 +9943,7 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>PR, RT.</t>
+          <t>PR, RT</t>
         </is>
       </c>
       <c r="S81" t="n">
@@ -10177,11 +10177,11 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -10294,11 +10294,11 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>Plasma or serum</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -10407,7 +10407,7 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S85" t="n">
@@ -10520,7 +10520,7 @@
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S86" t="n">
@@ -10633,7 +10633,7 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S87" t="n">
@@ -10972,11 +10972,11 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -11085,7 +11085,7 @@
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S91" t="n">
@@ -11319,11 +11319,11 @@
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>487</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11432,11 +11432,11 @@
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>South Korea, Asia, and the Americas</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -11549,11 +11549,11 @@
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>2021-2024</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11662,7 +11662,7 @@
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S96" t="n">
@@ -11775,11 +11775,11 @@
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>env, gag, pol, protease, reverse transcriptase, and integrase</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -12126,11 +12126,11 @@
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -12243,11 +12243,11 @@
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -12594,11 +12594,11 @@
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>NRTIs, NNRTIs, PIs</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -12715,11 +12715,11 @@
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>ZDV, 3TC, NVP, lopinavir/ritonavir, EFV</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="R114" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>"Yes""""</t>
         </is>
       </c>
       <c r="S114" t="n">
@@ -13901,7 +13901,7 @@
       </c>
       <c r="R115" t="inlineStr">
         <is>
-          <t>NGS</t>
+          <t>"NGS""""</t>
         </is>
       </c>
       <c r="S115" t="n">
@@ -14022,7 +14022,7 @@
       </c>
       <c r="R116" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>"Plasma""""</t>
         </is>
       </c>
       <c r="S116" t="n">
@@ -14143,7 +14143,7 @@
       </c>
       <c r="R117" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>"Yes""""</t>
         </is>
       </c>
       <c r="S117" t="n">
@@ -14264,7 +14264,7 @@
       </c>
       <c r="R118" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>"No""""</t>
         </is>
       </c>
       <c r="S118" t="n">
@@ -14385,7 +14385,7 @@
       </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>"Yes""""</t>
         </is>
       </c>
       <c r="S119" t="n">
@@ -14506,7 +14506,7 @@
       </c>
       <c r="R120" t="inlineStr">
         <is>
-          <t>NNRTIs</t>
+          <t>"NNRTIs, NRTIs""""</t>
         </is>
       </c>
       <c r="S120" t="n">
@@ -14627,7 +14627,7 @@
       </c>
       <c r="R121" t="inlineStr">
         <is>
-          <t>Efavirenz (EFV), Nevirapine (NVP), Lamivudine (3TC)</t>
+          <t>"Not reported"</t>
         </is>
       </c>
       <c r="S121" t="n">
@@ -14748,7 +14748,7 @@
       </c>
       <c r="R122" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>"No""""</t>
         </is>
       </c>
       <c r="S122" t="n">
@@ -14869,7 +14869,7 @@
       </c>
       <c r="R123" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>"No""""</t>
         </is>
       </c>
       <c r="S123" t="n">
@@ -15111,7 +15111,7 @@
       </c>
       <c r="R125" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>"20""""</t>
         </is>
       </c>
       <c r="S125" t="n">
@@ -15232,7 +15232,7 @@
       </c>
       <c r="R126" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>"Ghana""""</t>
         </is>
       </c>
       <c r="S126" t="n">
@@ -15353,7 +15353,7 @@
       </c>
       <c r="R127" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>"Not reported""""</t>
         </is>
       </c>
       <c r="S127" t="n">
@@ -15474,7 +15474,7 @@
       </c>
       <c r="R128" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>"No""""</t>
         </is>
       </c>
       <c r="S128" t="n">
@@ -15595,7 +15595,7 @@
       </c>
       <c r="R129" t="inlineStr">
         <is>
-          <t>PR, RT</t>
+          <t>"PR, RT""""</t>
         </is>
       </c>
       <c r="S129" t="n">
@@ -15837,7 +15837,7 @@
       </c>
       <c r="R131" t="inlineStr">
         <is>
-          <t>Sanger sequencing and Next generation sequencing</t>
+          <t>Sanger sequencing, NGS</t>
         </is>
       </c>
       <c r="S131" t="n">
@@ -15958,7 +15958,7 @@
       </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t>Plasma and DBS</t>
+          <t>Plasma, DBS</t>
         </is>
       </c>
       <c r="S132" t="n">
@@ -16430,7 +16430,7 @@
       </c>
       <c r="R136" t="inlineStr">
         <is>
-          <t>INSTIs</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S136" t="n">
@@ -16551,7 +16551,7 @@
       </c>
       <c r="R137" t="inlineStr">
         <is>
-          <t>DTG, TDF, 3TC</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S137" t="n">
@@ -17394,7 +17394,7 @@
       </c>
       <c r="R144" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S144" t="n">
@@ -17757,11 +17757,11 @@
       </c>
       <c r="R147" t="inlineStr">
         <is>
-          <t>NGS</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -17878,7 +17878,7 @@
       </c>
       <c r="R148" t="inlineStr">
         <is>
-          <t>Whole blood</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S148" t="n">
@@ -17999,7 +17999,7 @@
       </c>
       <c r="R149" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S149" t="n">
@@ -18120,11 +18120,11 @@
       </c>
       <c r="R150" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S150" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -18241,11 +18241,11 @@
       </c>
       <c r="R151" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -18362,11 +18362,11 @@
       </c>
       <c r="R152" t="inlineStr">
         <is>
-          <t>NRTIs, INSTIs, NNRTIs, PIs</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S152" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -18604,7 +18604,7 @@
       </c>
       <c r="R154" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S154" t="n">
@@ -18725,7 +18725,7 @@
       </c>
       <c r="R155" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S155" t="n">
@@ -18967,11 +18967,11 @@
       </c>
       <c r="R157" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S157" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -19330,7 +19330,7 @@
       </c>
       <c r="R160" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S160" t="n">
@@ -19451,11 +19451,11 @@
       </c>
       <c r="R161" t="inlineStr">
         <is>
-          <t>PR, RT, IN</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S161" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T161" t="inlineStr">
         <is>
@@ -19572,7 +19572,7 @@
       </c>
       <c r="R162" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>**Yes**</t>
         </is>
       </c>
       <c r="S162" t="n">
@@ -19693,7 +19693,7 @@
       </c>
       <c r="R163" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>**Sanger sequencing**</t>
         </is>
       </c>
       <c r="S163" t="n">
@@ -19814,7 +19814,7 @@
       </c>
       <c r="R164" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>**Plasma**</t>
         </is>
       </c>
       <c r="S164" t="n">
@@ -19935,7 +19935,7 @@
       </c>
       <c r="R165" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>**Yes**</t>
         </is>
       </c>
       <c r="S165" t="n">
@@ -20056,7 +20056,7 @@
       </c>
       <c r="R166" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>**No**</t>
         </is>
       </c>
       <c r="S166" t="n">
@@ -20177,7 +20177,7 @@
       </c>
       <c r="R167" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>**Yes**</t>
         </is>
       </c>
       <c r="S167" t="n">
@@ -20540,7 +20540,7 @@
       </c>
       <c r="R170" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>**No**</t>
         </is>
       </c>
       <c r="S170" t="n">
@@ -20661,7 +20661,7 @@
       </c>
       <c r="R171" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>**No**</t>
         </is>
       </c>
       <c r="S171" t="n">
@@ -20782,7 +20782,7 @@
       </c>
       <c r="R172" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>**Not reported**</t>
         </is>
       </c>
       <c r="S172" t="n">
@@ -20903,7 +20903,7 @@
       </c>
       <c r="R173" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>**212**</t>
         </is>
       </c>
       <c r="S173" t="n">
@@ -21024,7 +21024,7 @@
       </c>
       <c r="R174" t="inlineStr">
         <is>
-          <t>Malawi</t>
+          <t>**Malawi**</t>
         </is>
       </c>
       <c r="S174" t="n">
@@ -21145,7 +21145,7 @@
       </c>
       <c r="R175" t="inlineStr">
         <is>
-          <t>2022-2023</t>
+          <t>**2022-2023**</t>
         </is>
       </c>
       <c r="S175" t="n">
@@ -21266,7 +21266,7 @@
       </c>
       <c r="R176" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>**No**</t>
         </is>
       </c>
       <c r="S176" t="n">
@@ -21387,7 +21387,7 @@
       </c>
       <c r="R177" t="inlineStr">
         <is>
-          <t>PR, RT, IN</t>
+          <t>**PR, RT, IN**</t>
         </is>
       </c>
       <c r="S177" t="n">
@@ -21750,11 +21750,11 @@
       </c>
       <c r="R180" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S180" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T180" t="inlineStr">
         <is>
@@ -22109,11 +22109,11 @@
       </c>
       <c r="R183" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="S183" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T183" t="inlineStr">
         <is>
@@ -22230,11 +22230,11 @@
       </c>
       <c r="R184" t="inlineStr">
         <is>
-          <t>INSTIs, NRTIs, NNRTIs</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S184" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T184" t="inlineStr">
         <is>
@@ -22351,11 +22351,11 @@
       </c>
       <c r="R185" t="inlineStr">
         <is>
-          <t>Dolutegravir, emtricitabine, tenofovir disoproxil fumarate, bictegravir, emtricitabine, tenofovir alafenamide</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S185" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>
@@ -22472,11 +22472,11 @@
       </c>
       <c r="R186" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S186" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>
@@ -22831,7 +22831,7 @@
       </c>
       <c r="R189" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S189" t="n">
@@ -23436,7 +23436,7 @@
       </c>
       <c r="R194" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>**Yes**</t>
         </is>
       </c>
       <c r="S194" t="n">
@@ -23557,7 +23557,7 @@
       </c>
       <c r="R195" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>**Not reported**</t>
         </is>
       </c>
       <c r="S195" t="n">
@@ -23678,11 +23678,11 @@
       </c>
       <c r="R196" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>**Not reported**</t>
         </is>
       </c>
       <c r="S196" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T196" t="inlineStr">
         <is>
@@ -23799,7 +23799,7 @@
       </c>
       <c r="R197" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>**Yes**</t>
         </is>
       </c>
       <c r="S197" t="n">
@@ -23920,7 +23920,7 @@
       </c>
       <c r="R198" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>**No**</t>
         </is>
       </c>
       <c r="S198" t="n">
@@ -24041,7 +24041,7 @@
       </c>
       <c r="R199" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>**Yes**</t>
         </is>
       </c>
       <c r="S199" t="n">
@@ -24162,11 +24162,11 @@
       </c>
       <c r="R200" t="inlineStr">
         <is>
-          <t>NRTIs, NNRTIs, PIs, INSTIs</t>
+          <t>**Not reported**</t>
         </is>
       </c>
       <c r="S200" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T200" t="inlineStr">
         <is>
@@ -24283,11 +24283,11 @@
       </c>
       <c r="R201" t="inlineStr">
         <is>
-          <t>3TC, FTC, AZT, TDF, EFV, NVP, DTG</t>
+          <t>**Not reported**</t>
         </is>
       </c>
       <c r="S201" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T201" t="inlineStr">
         <is>
@@ -24404,7 +24404,7 @@
       </c>
       <c r="R202" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>**No**</t>
         </is>
       </c>
       <c r="S202" t="n">
@@ -24525,7 +24525,7 @@
       </c>
       <c r="R203" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>**No**</t>
         </is>
       </c>
       <c r="S203" t="n">
@@ -24646,7 +24646,7 @@
       </c>
       <c r="R204" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>**Not reported**</t>
         </is>
       </c>
       <c r="S204" t="n">
@@ -24767,7 +24767,7 @@
       </c>
       <c r="R205" t="inlineStr">
         <is>
-          <t>9685</t>
+          <t>**9685**</t>
         </is>
       </c>
       <c r="S205" t="n">
@@ -24888,7 +24888,7 @@
       </c>
       <c r="R206" t="inlineStr">
         <is>
-          <t>Tanzania</t>
+          <t>**Tanzania**</t>
         </is>
       </c>
       <c r="S206" t="n">
@@ -25009,11 +25009,11 @@
       </c>
       <c r="R207" t="inlineStr">
         <is>
-          <t>2004-2024</t>
+          <t>**Not reported**</t>
         </is>
       </c>
       <c r="S207" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T207" t="inlineStr">
         <is>
@@ -25130,7 +25130,7 @@
       </c>
       <c r="R208" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>**Not reported**</t>
         </is>
       </c>
       <c r="S208" t="n">
@@ -25251,11 +25251,11 @@
       </c>
       <c r="R209" t="inlineStr">
         <is>
-          <t>RT, PR</t>
+          <t>**Not reported**</t>
         </is>
       </c>
       <c r="S209" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T209" t="inlineStr">
         <is>
@@ -25372,7 +25372,7 @@
       </c>
       <c r="R210" t="inlineStr">
         <is>
-          <t>Yes.</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="S210" t="n">
@@ -25485,7 +25485,7 @@
       </c>
       <c r="R211" t="inlineStr">
         <is>
-          <t>Sanger sequencing.</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="S211" t="n">
@@ -25602,7 +25602,7 @@
       </c>
       <c r="R212" t="inlineStr">
         <is>
-          <t>Plasma.</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="S212" t="n">
@@ -25719,7 +25719,7 @@
       </c>
       <c r="R213" t="inlineStr">
         <is>
-          <t>No.</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S213" t="n">
@@ -25836,7 +25836,7 @@
       </c>
       <c r="R214" t="inlineStr">
         <is>
-          <t>No.</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S214" t="n">
@@ -25953,7 +25953,7 @@
       </c>
       <c r="R215" t="inlineStr">
         <is>
-          <t>No.</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S215" t="n">
@@ -26074,7 +26074,7 @@
       </c>
       <c r="R216" t="inlineStr">
         <is>
-          <t>None.</t>
+          <t>None</t>
         </is>
       </c>
       <c r="S216" t="n">
@@ -26187,7 +26187,7 @@
       </c>
       <c r="R217" t="inlineStr">
         <is>
-          <t>None.</t>
+          <t>None</t>
         </is>
       </c>
       <c r="S217" t="n">
@@ -26300,7 +26300,7 @@
       </c>
       <c r="R218" t="inlineStr">
         <is>
-          <t>No.</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S218" t="n">
@@ -26417,7 +26417,7 @@
       </c>
       <c r="R219" t="inlineStr">
         <is>
-          <t>Yes.</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="S219" t="n">
@@ -26655,11 +26655,11 @@
       </c>
       <c r="R221" t="inlineStr">
         <is>
-          <t>1,159.00</t>
+          <t>1048</t>
         </is>
       </c>
       <c r="S221" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T221" t="inlineStr">
         <is>
@@ -26772,7 +26772,7 @@
       </c>
       <c r="R222" t="inlineStr">
         <is>
-          <t>China.</t>
+          <t>China</t>
         </is>
       </c>
       <c r="S222" t="n">
@@ -26893,7 +26893,7 @@
       </c>
       <c r="R223" t="inlineStr">
         <is>
-          <t>2019-2022.</t>
+          <t>2019-2022</t>
         </is>
       </c>
       <c r="S223" t="n">
@@ -27014,7 +27014,7 @@
       </c>
       <c r="R224" t="inlineStr">
         <is>
-          <t>No.</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S224" t="n">
@@ -27127,7 +27127,7 @@
       </c>
       <c r="R225" t="inlineStr">
         <is>
-          <t>PR, RT.</t>
+          <t>PR, RT</t>
         </is>
       </c>
       <c r="S225" t="n">
@@ -27474,7 +27474,7 @@
       </c>
       <c r="R228" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S228" t="n">
@@ -27591,7 +27591,7 @@
       </c>
       <c r="R229" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S229" t="n">
@@ -27704,7 +27704,7 @@
       </c>
       <c r="R230" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S230" t="n">
@@ -27817,7 +27817,7 @@
       </c>
       <c r="R231" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S231" t="n">
@@ -28955,11 +28955,11 @@
       </c>
       <c r="R241" t="inlineStr">
         <is>
-          <t>Gag-Pol, Env-Nef</t>
+          <t>Env, NC, IN</t>
         </is>
       </c>
       <c r="S241" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T241" t="inlineStr">
         <is>
@@ -29306,11 +29306,11 @@
       </c>
       <c r="R244" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S244" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T244" t="inlineStr">
         <is>
@@ -29540,11 +29540,11 @@
       </c>
       <c r="R246" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S246" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T246" t="inlineStr">
         <is>
@@ -30004,11 +30004,11 @@
       </c>
       <c r="R250" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S250" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T250" t="inlineStr">
         <is>
@@ -30125,7 +30125,7 @@
       </c>
       <c r="R251" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S251" t="n">
@@ -30363,11 +30363,11 @@
       </c>
       <c r="R253" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S253" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T253" t="inlineStr">
         <is>
@@ -30718,11 +30718,11 @@
       </c>
       <c r="R256" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S256" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T256" t="inlineStr">
         <is>
@@ -30839,7 +30839,7 @@
       </c>
       <c r="R257" t="inlineStr">
         <is>
-          <t>gag, protease</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S257" t="n">
@@ -30960,7 +30960,7 @@
       </c>
       <c r="R258" t="inlineStr">
         <is>
-          <t>Yes.</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="S258" t="n">
@@ -31077,11 +31077,11 @@
       </c>
       <c r="R259" t="inlineStr">
         <is>
-          <t>Not reported (but likely Sanger sequencing or NGS).</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="S259" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T259" t="inlineStr">
         <is>
@@ -31194,7 +31194,7 @@
       </c>
       <c r="R260" t="inlineStr">
         <is>
-          <t>Whole blood.</t>
+          <t>Whole blood</t>
         </is>
       </c>
       <c r="S260" t="n">
@@ -31315,11 +31315,11 @@
       </c>
       <c r="R261" t="inlineStr">
         <is>
-          <t>Yes.</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S261" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T261" t="inlineStr">
         <is>
@@ -31432,7 +31432,7 @@
       </c>
       <c r="R262" t="inlineStr">
         <is>
-          <t>Yes.</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="S262" t="n">
@@ -31549,7 +31549,7 @@
       </c>
       <c r="R263" t="inlineStr">
         <is>
-          <t>Yes.</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="S263" t="n">
@@ -31666,7 +31666,7 @@
       </c>
       <c r="R264" t="inlineStr">
         <is>
-          <t>Not reported.</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S264" t="n">
@@ -31787,7 +31787,7 @@
       </c>
       <c r="R265" t="inlineStr">
         <is>
-          <t>Not reported.</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S265" t="n">
@@ -31904,7 +31904,7 @@
       </c>
       <c r="R266" t="inlineStr">
         <is>
-          <t>No.</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S266" t="n">
@@ -32021,7 +32021,7 @@
       </c>
       <c r="R267" t="inlineStr">
         <is>
-          <t>Not reported.</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S267" t="n">
@@ -32263,7 +32263,7 @@
       </c>
       <c r="R269" t="inlineStr">
         <is>
-          <t>241</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S269" t="n">
@@ -32380,7 +32380,7 @@
       </c>
       <c r="R270" t="inlineStr">
         <is>
-          <t>Not reported.</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S270" t="n">
@@ -32501,11 +32501,11 @@
       </c>
       <c r="R271" t="inlineStr">
         <is>
-          <t>1997-2019.</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S271" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T271" t="inlineStr">
         <is>
@@ -32622,7 +32622,7 @@
       </c>
       <c r="R272" t="inlineStr">
         <is>
-          <t>Not reported.</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S272" t="n">
@@ -32739,7 +32739,7 @@
       </c>
       <c r="R273" t="inlineStr">
         <is>
-          <t>PR, RT, IN.</t>
+          <t>PR, RT, IN</t>
         </is>
       </c>
       <c r="S273" t="n">
@@ -33102,11 +33102,11 @@
       </c>
       <c r="R276" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S276" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T276" t="inlineStr">
         <is>
@@ -33328,7 +33328,7 @@
       </c>
       <c r="R278" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S278" t="n">
@@ -33675,7 +33675,7 @@
       </c>
       <c r="R281" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>None</t>
         </is>
       </c>
       <c r="S281" t="n">
@@ -34038,7 +34038,7 @@
       </c>
       <c r="R284" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Not reported</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S284" t="n">
@@ -34159,11 +34159,11 @@
       </c>
       <c r="R285" t="inlineStr">
         <is>
-          <t>1182</t>
+          <t>1106</t>
         </is>
       </c>
       <c r="S285" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T285" t="inlineStr">
         <is>
@@ -34522,7 +34522,7 @@
       </c>
       <c r="R288" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S288" t="n">
@@ -34643,7 +34643,7 @@
       </c>
       <c r="R289" t="inlineStr">
         <is>
-          <t>All HIV genes (PR, RT, IN, Pol, CA, Env)</t>
+          <t>All genes</t>
         </is>
       </c>
       <c r="S289" t="n">
@@ -34760,11 +34760,11 @@
       </c>
       <c r="R290" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="S290" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T290" t="inlineStr">
         <is>
@@ -35123,11 +35123,11 @@
       </c>
       <c r="R293" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="S293" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T293" t="inlineStr">
         <is>
@@ -35365,11 +35365,11 @@
       </c>
       <c r="R295" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="S295" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T295" t="inlineStr">
         <is>
@@ -36087,11 +36087,11 @@
       </c>
       <c r="R301" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>249</t>
         </is>
       </c>
       <c r="S301" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T301" t="inlineStr">
         <is>
@@ -36208,11 +36208,11 @@
       </c>
       <c r="R302" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="S302" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T302" t="inlineStr">
         <is>
@@ -36692,7 +36692,7 @@
       </c>
       <c r="R306" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>"Yes"</t>
         </is>
       </c>
       <c r="S306" t="n">
@@ -36813,7 +36813,7 @@
       </c>
       <c r="R307" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>"Sanger sequencing"</t>
         </is>
       </c>
       <c r="S307" t="n">
@@ -36934,7 +36934,7 @@
       </c>
       <c r="R308" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>"Plasma"</t>
         </is>
       </c>
       <c r="S308" t="n">
@@ -37055,7 +37055,7 @@
       </c>
       <c r="R309" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>"Yes"</t>
         </is>
       </c>
       <c r="S309" t="n">
@@ -37176,7 +37176,7 @@
       </c>
       <c r="R310" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>"No"</t>
         </is>
       </c>
       <c r="S310" t="n">
@@ -37297,7 +37297,7 @@
       </c>
       <c r="R311" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>"Yes"</t>
         </is>
       </c>
       <c r="S311" t="n">
@@ -37418,7 +37418,7 @@
       </c>
       <c r="R312" t="inlineStr">
         <is>
-          <t>INSTIs</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S312" t="n">
@@ -37539,11 +37539,11 @@
       </c>
       <c r="R313" t="inlineStr">
         <is>
-          <t>DTG</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S313" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T313" t="inlineStr">
         <is>
@@ -37660,7 +37660,7 @@
       </c>
       <c r="R314" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>"No"</t>
         </is>
       </c>
       <c r="S314" t="n">
@@ -37781,7 +37781,7 @@
       </c>
       <c r="R315" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>"No"</t>
         </is>
       </c>
       <c r="S315" t="n">
@@ -37902,7 +37902,7 @@
       </c>
       <c r="R316" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>"Not reported"</t>
         </is>
       </c>
       <c r="S316" t="n">
@@ -38023,7 +38023,7 @@
       </c>
       <c r="R317" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>"28"</t>
         </is>
       </c>
       <c r="S317" t="n">
@@ -38136,7 +38136,7 @@
       </c>
       <c r="R318" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>"Mozambique"</t>
         </is>
       </c>
       <c r="S318" t="n">
@@ -38257,7 +38257,7 @@
       </c>
       <c r="R319" t="inlineStr">
         <is>
-          <t>2023-2024</t>
+          <t>"2022-2024"</t>
         </is>
       </c>
       <c r="S319" t="n">
@@ -38374,7 +38374,7 @@
       </c>
       <c r="R320" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>"No"</t>
         </is>
       </c>
       <c r="S320" t="n">
@@ -38495,7 +38495,7 @@
       </c>
       <c r="R321" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>"IN"</t>
         </is>
       </c>
       <c r="S321" t="n">
@@ -39092,7 +39092,7 @@
       </c>
       <c r="R326" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S326" t="n">
@@ -39326,11 +39326,11 @@
       </c>
       <c r="R328" t="inlineStr">
         <is>
-          <t>NRTIs, NNRTIs, PIs</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S328" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T328" t="inlineStr">
         <is>
@@ -39447,11 +39447,11 @@
       </c>
       <c r="R329" t="inlineStr">
         <is>
-          <t>ABC, 3TC, EFV, NVP, TDF, AZT, DTG, ATV, LPV</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S329" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T329" t="inlineStr">
         <is>
@@ -39568,11 +39568,11 @@
       </c>
       <c r="R330" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S330" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T330" t="inlineStr">
         <is>
@@ -40286,7 +40286,7 @@
       </c>
       <c r="R336" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S336" t="n">
@@ -40875,11 +40875,11 @@
       </c>
       <c r="R341" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S341" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T341" t="inlineStr">
         <is>
@@ -40992,11 +40992,11 @@
       </c>
       <c r="R342" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S342" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T342" t="inlineStr">
         <is>
@@ -41109,7 +41109,7 @@
       </c>
       <c r="R343" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S343" t="n">
@@ -41444,11 +41444,11 @@
       </c>
       <c r="R346" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S346" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T346" t="inlineStr">
         <is>
@@ -41561,7 +41561,7 @@
       </c>
       <c r="R347" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S347" t="n">
@@ -41803,7 +41803,7 @@
       </c>
       <c r="R349" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S349" t="n">
@@ -41916,11 +41916,11 @@
       </c>
       <c r="R350" t="inlineStr">
         <is>
-          <t>USA, Dominican Republic</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S350" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T350" t="inlineStr">
         <is>
@@ -42033,11 +42033,11 @@
       </c>
       <c r="R351" t="inlineStr">
         <is>
-          <t>2019-2020</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S351" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T351" t="inlineStr">
         <is>
@@ -42267,11 +42267,11 @@
       </c>
       <c r="R353" t="inlineStr">
         <is>
-          <t>CA (capsid)</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S353" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T353" t="inlineStr">
         <is>
@@ -42388,7 +42388,7 @@
       </c>
       <c r="R354" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>"Yes"</t>
         </is>
       </c>
       <c r="S354" t="n">
@@ -42509,7 +42509,7 @@
       </c>
       <c r="R355" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>"Not reported"</t>
         </is>
       </c>
       <c r="S355" t="n">
@@ -42630,11 +42630,11 @@
       </c>
       <c r="R356" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>"Not reported"</t>
         </is>
       </c>
       <c r="S356" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T356" t="inlineStr">
         <is>
@@ -42751,7 +42751,7 @@
       </c>
       <c r="R357" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>"Yes"</t>
         </is>
       </c>
       <c r="S357" t="n">
@@ -42872,7 +42872,7 @@
       </c>
       <c r="R358" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>"No"</t>
         </is>
       </c>
       <c r="S358" t="n">
@@ -42993,7 +42993,7 @@
       </c>
       <c r="R359" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>"Yes"</t>
         </is>
       </c>
       <c r="S359" t="n">
@@ -43114,11 +43114,11 @@
       </c>
       <c r="R360" t="inlineStr">
         <is>
-          <t>NRTIs, NNRTIs, PIs</t>
+          <t>"Not reported"</t>
         </is>
       </c>
       <c r="S360" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T360" t="inlineStr">
         <is>
@@ -43235,7 +43235,7 @@
       </c>
       <c r="R361" t="inlineStr">
         <is>
-          <t>AZT, TDF, NNRTIs</t>
+          <t>"Not reported"</t>
         </is>
       </c>
       <c r="S361" t="n">
@@ -43356,7 +43356,7 @@
       </c>
       <c r="R362" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>"No"</t>
         </is>
       </c>
       <c r="S362" t="n">
@@ -43477,7 +43477,7 @@
       </c>
       <c r="R363" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>"No"</t>
         </is>
       </c>
       <c r="S363" t="n">
@@ -43598,7 +43598,7 @@
       </c>
       <c r="R364" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>"Not reported"</t>
         </is>
       </c>
       <c r="S364" t="n">
@@ -43719,7 +43719,7 @@
       </c>
       <c r="R365" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>"235"</t>
         </is>
       </c>
       <c r="S365" t="n">
@@ -43840,7 +43840,7 @@
       </c>
       <c r="R366" t="inlineStr">
         <is>
-          <t>Uganda</t>
+          <t>"Uganda"</t>
         </is>
       </c>
       <c r="S366" t="n">
@@ -43961,7 +43961,7 @@
       </c>
       <c r="R367" t="inlineStr">
         <is>
-          <t>2018-2023</t>
+          <t>"2018-2023"</t>
         </is>
       </c>
       <c r="S367" t="n">
@@ -44082,7 +44082,7 @@
       </c>
       <c r="R368" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>"Not reported"</t>
         </is>
       </c>
       <c r="S368" t="n">
@@ -44203,11 +44203,11 @@
       </c>
       <c r="R369" t="inlineStr">
         <is>
-          <t>PR, RT, IN</t>
+          <t>"Not reported"</t>
         </is>
       </c>
       <c r="S369" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T369" t="inlineStr">
         <is>
@@ -44558,7 +44558,7 @@
       </c>
       <c r="R372" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Plasma, Whole blood</t>
         </is>
       </c>
       <c r="S372" t="n">
@@ -45486,11 +45486,11 @@
       </c>
       <c r="R380" t="inlineStr">
         <is>
-          <t>PV187006</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S380" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T380" t="inlineStr">
         <is>
@@ -46071,11 +46071,11 @@
       </c>
       <c r="R385" t="inlineStr">
         <is>
-          <t>Pol, Env</t>
+          <t>Full genome</t>
         </is>
       </c>
       <c r="S385" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T385" t="inlineStr">
         <is>
@@ -46188,11 +46188,11 @@
       </c>
       <c r="R386" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="S386" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T386" t="inlineStr">
         <is>
@@ -47120,11 +47120,11 @@
       </c>
       <c r="R394" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S394" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T394" t="inlineStr">
         <is>
@@ -47237,7 +47237,7 @@
       </c>
       <c r="R395" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S395" t="n">
@@ -47935,11 +47935,11 @@
       </c>
       <c r="R401" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S401" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T401" t="inlineStr">
         <is>
@@ -48282,11 +48282,11 @@
       </c>
       <c r="R404" t="inlineStr">
         <is>
-          <t>Infectious clones</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S404" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T404" t="inlineStr">
         <is>
@@ -48403,7 +48403,7 @@
       </c>
       <c r="R405" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S405" t="n">
@@ -48637,7 +48637,7 @@
       </c>
       <c r="R407" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S407" t="n">
@@ -48988,11 +48988,11 @@
       </c>
       <c r="R410" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S410" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T410" t="inlineStr">
         <is>
@@ -49105,11 +49105,11 @@
       </c>
       <c r="R411" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S411" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T411" t="inlineStr">
         <is>
@@ -49226,11 +49226,11 @@
       </c>
       <c r="R412" t="inlineStr">
         <is>
-          <t>PQ735970-PQ735985</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S412" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T412" t="inlineStr">
         <is>
@@ -49343,7 +49343,7 @@
       </c>
       <c r="R413" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S413" t="n">
@@ -49460,7 +49460,7 @@
       </c>
       <c r="R414" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S414" t="n">
@@ -49581,7 +49581,7 @@
       </c>
       <c r="R415" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S415" t="n">
@@ -49698,11 +49698,11 @@
       </c>
       <c r="R416" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S416" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T416" t="inlineStr">
         <is>
@@ -49811,11 +49811,11 @@
       </c>
       <c r="R417" t="inlineStr">
         <is>
-          <t>Pol</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S417" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T417" t="inlineStr">
         <is>
@@ -50174,7 +50174,7 @@
       </c>
       <c r="R420" t="inlineStr">
         <is>
-          <t>DBS and venous blood</t>
+          <t>DBS, Plasma</t>
         </is>
       </c>
       <c r="S420" t="n">
@@ -51594,7 +51594,7 @@
       </c>
       <c r="R432" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S432" t="n">
@@ -51836,7 +51836,7 @@
       </c>
       <c r="R434" t="inlineStr">
         <is>
-          <t>Yes.</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="S434" t="n">
@@ -51949,7 +51949,7 @@
       </c>
       <c r="R435" t="inlineStr">
         <is>
-          <t>Sanger sequencing.</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="S435" t="n">
@@ -52062,7 +52062,7 @@
       </c>
       <c r="R436" t="inlineStr">
         <is>
-          <t>Plasma.</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="S436" t="n">
@@ -52175,7 +52175,7 @@
       </c>
       <c r="R437" t="inlineStr">
         <is>
-          <t>Yes.</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="S437" t="n">
@@ -52288,7 +52288,7 @@
       </c>
       <c r="R438" t="inlineStr">
         <is>
-          <t>Not reported.</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S438" t="n">
@@ -52401,7 +52401,7 @@
       </c>
       <c r="R439" t="inlineStr">
         <is>
-          <t>Yes.</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="S439" t="n">
@@ -52514,11 +52514,11 @@
       </c>
       <c r="R440" t="inlineStr">
         <is>
-          <t>NRTIs, NNRTIs, PIs, and INSTIs.</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S440" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T440" t="inlineStr">
         <is>
@@ -52631,11 +52631,11 @@
       </c>
       <c r="R441" t="inlineStr">
         <is>
-          <t>DTG, ABC, AZT, TDF, LPV, and EFV.</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S441" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T441" t="inlineStr">
         <is>
@@ -52748,11 +52748,11 @@
       </c>
       <c r="R442" t="inlineStr">
         <is>
-          <t>Yes.</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S442" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T442" t="inlineStr">
         <is>
@@ -52861,7 +52861,7 @@
       </c>
       <c r="R443" t="inlineStr">
         <is>
-          <t>No.</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S443" t="n">
@@ -53196,7 +53196,7 @@
       </c>
       <c r="R446" t="inlineStr">
         <is>
-          <t>Uganda.</t>
+          <t>Uganda</t>
         </is>
       </c>
       <c r="S446" t="n">
@@ -53422,7 +53422,7 @@
       </c>
       <c r="R448" t="inlineStr">
         <is>
-          <t>Not reported.</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S448" t="n">
@@ -53531,11 +53531,11 @@
       </c>
       <c r="R449" t="inlineStr">
         <is>
-          <t>PR, RT, and possibly others.</t>
+          <t>PR, RT, IN</t>
         </is>
       </c>
       <c r="S449" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T449" t="inlineStr">
         <is>
@@ -53765,11 +53765,11 @@
       </c>
       <c r="R451" t="inlineStr">
         <is>
-          <t>NGS</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S451" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T451" t="inlineStr">
         <is>
@@ -53886,11 +53886,11 @@
       </c>
       <c r="R452" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S452" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T452" t="inlineStr">
         <is>
@@ -54007,11 +54007,11 @@
       </c>
       <c r="R453" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S453" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T453" t="inlineStr">
         <is>
@@ -54128,11 +54128,11 @@
       </c>
       <c r="R454" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S454" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T454" t="inlineStr">
         <is>
@@ -54249,11 +54249,11 @@
       </c>
       <c r="R455" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S455" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T455" t="inlineStr">
         <is>
@@ -54366,7 +54366,7 @@
       </c>
       <c r="R456" t="inlineStr">
         <is>
-          <t>NRTIs, capsid inhibitors</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S456" t="n">
@@ -54487,11 +54487,11 @@
       </c>
       <c r="R457" t="inlineStr">
         <is>
-          <t>lenacapavir, emtricitabine/tenofovir alafenamide, emtricitabine/tenofovir disoproxil fumarate</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S457" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T457" t="inlineStr">
         <is>
@@ -54967,7 +54967,7 @@
       </c>
       <c r="R461" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>77</t>
         </is>
       </c>
       <c r="S461" t="n">
@@ -55447,11 +55447,11 @@
       </c>
       <c r="R465" t="inlineStr">
         <is>
-          <t>CA, PR, RT, IN</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S465" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T465" t="inlineStr">
         <is>
@@ -56524,7 +56524,7 @@
       </c>
       <c r="R474" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S474" t="n">
@@ -56645,11 +56645,11 @@
       </c>
       <c r="R475" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S475" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T475" t="inlineStr">
         <is>
@@ -57004,11 +57004,11 @@
       </c>
       <c r="R478" t="inlineStr">
         <is>
-          <t>Kenya, Uganda, Tanzania, and Ethiopia</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S478" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T478" t="inlineStr">
         <is>
@@ -57125,11 +57125,11 @@
       </c>
       <c r="R479" t="inlineStr">
         <is>
-          <t>2015-2025</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S479" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T479" t="inlineStr">
         <is>
@@ -57363,11 +57363,11 @@
       </c>
       <c r="R481" t="inlineStr">
         <is>
-          <t>PR, RT, IN</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="S481" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T481" t="inlineStr">
         <is>
